--- a/inst/extdata/temp_field.xlsx
+++ b/inst/extdata/temp_field.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FangCloudSync\R_WD360\Project\soyplant\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FangCloudSync\R_WD360\Project\soyplant\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0C1380-362F-4DCA-B7A2-FF9D420CE505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A466619B-09E7-421E-B63C-3CC5137FBC90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3795" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -223,6 +223,14 @@
   </si>
   <si>
     <t>前田间识别号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>former_stageid</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>前阶段号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -591,18 +599,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.6640625" style="2"/>
-    <col min="4" max="4" width="28.08203125" customWidth="1"/>
+    <col min="4" max="4" width="28.06640625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
@@ -619,7 +627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -636,7 +644,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -653,7 +661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -670,7 +678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -687,7 +695,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -704,7 +712,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -721,7 +729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -738,7 +746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -755,7 +763,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -772,7 +780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -789,7 +797,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -806,7 +814,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -823,7 +831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -840,7 +848,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -857,7 +865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -874,7 +882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -891,7 +899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -908,29 +916,29 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C19" s="5">
         <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="5">
         <v>19</v>
@@ -939,15 +947,15 @@
         <v>35</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="5">
         <v>20</v>
@@ -956,15 +964,15 @@
         <v>35</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="5">
         <v>21</v>
@@ -973,15 +981,15 @@
         <v>35</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="5">
         <v>22</v>
@@ -990,15 +998,15 @@
         <v>35</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="5">
         <v>23</v>
@@ -1007,6 +1015,23 @@
         <v>35</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="5">
+        <v>24</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>47</v>
       </c>
     </row>
